--- a/capstone-docs/rp_2.1_project-tracking/Report_2.1_Project_Tracking_IeltsPath_v1.xlsx
+++ b/capstone-docs/rp_2.1_project-tracking/Report_2.1_Project_Tracking_IeltsPath_v1.xlsx
@@ -463,7 +463,7 @@
     <t>LinhNDM</t>
   </si>
   <si>
-    <t>SonLT</t>
+    <t xml:space="preserve">SonLH</t>
   </si>
   <si>
     <t>TungVPH</t>
@@ -484,7 +484,7 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>Start date: Report 1; participation estimated.</t>
+    <t xml:space="preserve">Kick-off meeting (group minutes 10/09/2026).</t>
   </si>
   <si>
     <t>FE 241abca.</t>
@@ -892,7 +892,7 @@
     <t>Stage 1</t>
   </si>
   <si>
-    <t>Report 1 (Project Introduction)</t>
+    <t xml:space="preserve">Report 1 (Vision &amp; Scope)</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -910,7 +910,7 @@
     <t>Stage 3</t>
   </si>
   <si>
-    <t>SDS v1.0 + Test Planning</t>
+    <t xml:space="preserve">TDS v1.0 + Test Planning</t>
   </si>
   <si>
     <t>Week 5</t>
@@ -1006,7 +1006,7 @@
     <t>1.1</t>
   </si>
   <si>
-    <t>Report 1 — Project Introduction</t>
+    <t xml:space="preserve">Report 1 — Vision &amp; Scope</t>
   </si>
   <si>
     <t xml:space="preserve">  Stage 2: Project Planning &amp; Initial Requirements (Weeks 2–3)</t>
@@ -1054,7 +1054,7 @@
     <t>3.3</t>
   </si>
   <si>
-    <t>Report 4 — SDS v1.0 (High Level Design)</t>
+    <t xml:space="preserve">Report 4 — TDS v1.0 (High Level Design)</t>
   </si>
   <si>
     <t>3.4</t>
@@ -1069,7 +1069,7 @@
     <t>4.1.1</t>
   </si>
   <si>
-    <t>Report 4 — SDS v1.1 (Detailed Design)</t>
+    <t xml:space="preserve">Report 4 — TDS v1.1 (Detailed Design)</t>
   </si>
   <si>
     <t>Week 6</t>
@@ -1114,7 +1114,7 @@
     <t>4.2.1</t>
   </si>
   <si>
-    <t>Report 4 — SDS v1.2</t>
+    <t xml:space="preserve">Report 4 — TDS v1.2</t>
   </si>
   <si>
     <t>Week 8</t>
@@ -1159,7 +1159,7 @@
     <t>4.3.1</t>
   </si>
   <si>
-    <t>Report 4 — SDS v1.3</t>
+    <t xml:space="preserve">Report 4 — TDS v1.3</t>
   </si>
   <si>
     <t>Week 10</t>
@@ -1351,7 +1351,7 @@
     <t>Gives the learner a dashboard of study time, four-skill progress, words to review, mentor feedback, courses and the study streak. Route: /overview · RequireAuth (default route when signed in)</t>
   </si>
   <si>
-    <t>SonLT</t>
+    <t xml:space="preserve">SonLH</t>
   </si>
   <si>
     <t>WBS-008 — Learning Path</t>
@@ -1852,7 +1852,7 @@
     <t>FT-44, FT-51, FT-53</t>
   </si>
   <si>
-    <t>Creates at most one study reminder per learner per day, at the learner's preferred local time, on days without a qualifying study activity. Trigger: @Scheduled every [TBC] minutes; ShedLock or SKIP LOCKED to run on one instance [TBC]</t>
+    <t>Creates at most one study reminder per learner per day, at the learner's preferred local time, on days without a qualifying study activity. Trigger: @Scheduled at an interval set when the job is built; ShedLock or SKIP LOCKED to run on one instance [TBC]</t>
   </si>
   <si>
     <t>WBS-063 — JOB-06 Notification delivery retry</t>
@@ -1861,7 +1861,7 @@
     <t>FT-52, FT-53, FT-54</t>
   </si>
   <si>
-    <t>Sends pending notification deliveries to Firebase Cloud Messaging or the Email Service and retries failed ones without creating a second notification. Trigger: @Scheduled every [TBC] s</t>
+    <t>Sends pending notification deliveries to Firebase Cloud Messaging or the Email Service and retries failed ones without creating a second notification. Trigger: @Scheduled at an interval set when the job is built</t>
   </si>
   <si>
     <t>WBS-064 — JOB-07 Matchmaking queue sweeper</t>
@@ -1870,7 +1870,7 @@
     <t>FT-47, FT-48</t>
   </si>
   <si>
-    <t>Groups waiting learners of the same game type into a room and starts the match, and removes learners who waited too long. Trigger: @Scheduled every [TBC] s</t>
+    <t>Groups waiting learners of the same game type into a room and starts the match, and removes learners who waited too long. Trigger: @Scheduled at an interval set when the job is built</t>
   </si>
   <si>
     <t>WBS-065 — Requirements and traceability baseline</t>
@@ -2146,7 +2146,7 @@
     <t>FE auth, learning, course and multi-skill alignment</t>
   </si>
   <si>
-    <t>SonLT / HieuLT</t>
+    <t xml:space="preserve">SonLH / HieuLT</t>
   </si>
   <si>
     <t>Nguyen Viet Hoang / hoangnv31 observed in Git.</t>
@@ -2332,7 +2332,7 @@
     <t>Source access</t>
   </si>
   <si>
-    <t>backend/capstone-docs; frontend/plans</t>
+    <t xml:space="preserve">project repository</t>
   </si>
   <si>
     <t>Read/reference</t>
@@ -2497,7 +2497,7 @@
     <t>Q-013</t>
   </si>
   <si>
-    <t>Should Speaking, full mock tests, mobile, games and community count as Phase 1 accepted features?</t>
+    <t>Should Speaking, full mock tests, games and community count as Phase 1 accepted features? (The mobile app left the scope in V&amp;S v1.1.0, LI-09.)</t>
   </si>
   <si>
     <t>They are product features in Vision &amp; Scope, but outside the priority test v1 boundary or lack full flow evidence. Confirm future delivery allocation; do not mark accepted from code presence alone.</t>
@@ -2659,7 +2659,7 @@
     <t>FE 6716dd9 (main 3b933051)</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005/fix-ux-cta-gates.md; frontend/plans/reports/e2e-practice-261005/report.md confirms gap closed; full fresh browser retest still open. | Assignment proposed from team roles; not a historical signed assignment. Fixed indicates documented code fix; separate browser retest required, not Closed.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026 confirms gap closed; full fresh browser retest still open. Retest in the browser before closing.</t>
   </si>
   <si>
     <t>D-002</t>
@@ -2680,7 +2680,7 @@
     <t>Assignment error handling</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005/fix-ux-cta-gates.md; frontend/plans/reports/e2e-practice-261005/report.md | Assignment proposed from team roles; not a historical signed assignment. Fixed indicates documented code fix; separate browser retest required, not Closed.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026. Retest in the browser before closing.</t>
   </si>
   <si>
     <t>D-003</t>
@@ -2701,7 +2701,7 @@
     <t>Topic ReviewGate / GET reviews</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005/fix-ux-cta-gates.md; frontend/plans/reports/e2e-practice-261005/report.md browser smoke only. | Assignment proposed from team roles; not a historical signed assignment. Fixed indicates documented code fix; separate browser retest required, not Closed.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026 browser smoke only. Retest in the browser before closing.</t>
   </si>
   <si>
     <t>D-004</t>
@@ -2722,7 +2722,7 @@
     <t>Auth and learning primary CTA</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005/fix-ux-cta-gates.md records layout fix, but frontend/plans/reports/e2e-main-flow-261005-fresh/report.md repeats observation. Application-wide reproduction is not established. | Assignment proposed from team roles; not a historical signed assignment. Verification concern retained; not a confirmed universal product failure.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026 records layout fix, but E2E test report 05/10/2026 repeats observation. Application-wide reproduction is not established. Keep open until it is reproduced or closed.</t>
   </si>
   <si>
     <t>D-005</t>
@@ -2743,7 +2743,7 @@
     <t>Result summary accessibility</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005/report.md item 5. Verify with a screen reader before confirming defect. | Assignment proposed from team roles; not a historical signed assignment.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026 item 5. Verify with a screen reader before confirming defect.</t>
   </si>
   <si>
     <t>D-006</t>
@@ -2839,7 +2839,7 @@
     <t>Acceptance and phase reporting may use different feature populations.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx; original WBS | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve">Test Plan (Report 5); original WBS</t>
   </si>
   <si>
     <t>I-002</t>
@@ -2857,7 +2857,7 @@
     <t>Validate the 48-row, 211.5-hour retrospective timesheet against member records, dates, hours and approval evidence. Review states are Pending, Submitted and Approved. See Q-014.</t>
   </si>
   <si>
-    <t>Original tracking workbook contains unrelated sample hours and reporter. | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>I-003</t>
@@ -2875,7 +2875,7 @@
     <t>Run without API gate clearance: lesson, first Practice submit, failed Practice review, pass test, next topic. Capture artifacts.</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005-fresh/report.md; frontend/plans/reports/e2e-practice-261005/report.md | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026</t>
   </si>
   <si>
     <t>I-004</t>
@@ -2890,7 +2890,7 @@
     <t>Review real essays against rubric and play configured audio; verify timeout, points retry and transcript visibility.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx; frontend/plans/reports/e2e-practice-261005/report.md | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve">Test Plan (Report 5); E2E test report 05/10/2026</t>
   </si>
   <si>
     <t>I-005</t>
@@ -2911,7 +2911,7 @@
     <t>Confirm free-only demo scope or implement entitlement checks as an approved follow-up before paid release.</t>
   </si>
   <si>
-    <t>backend/docs/fe-main-flow-guide.md §6; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve">frontend–backend flow guide §6; Test Plan (Report 5)</t>
   </si>
   <si>
     <t>I-007</t>
@@ -2923,7 +2923,7 @@
     <t>End-to-end course recommendation and course-test completion remain incomplete.</t>
   </si>
   <si>
-    <t>backend/plans/261006-2228-course-band-levels/plan.md final concerns; frontend/src/features/learning-path/api/learningApi.ts | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve">team design notes final concerns; frontend learning API</t>
   </si>
   <si>
     <t>I-008</t>
@@ -2950,7 +2950,7 @@
     <t>Reset UI is in Iteration 1; verify real email token delivery separately. OAuth remains Iteration 3 and unavailable until implementation/QA. Do not report either external flow as accepted.</t>
   </si>
   <si>
-    <t>frontend/docs/journals/2026-10-05-fe-auth-forgot-reset-wiring.md; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx | Owner/deadline are proposed resolution assignments.</t>
+    <t xml:space="preserve">frontend change note 05/10/2026; Test Plan (Report 5)</t>
   </si>
   <si>
     <t>Risks — IELTSPath Phase 1</t>
@@ -2986,7 +2986,7 @@
     <t>Replan approved changes and defer unaccepted extensions.</t>
   </si>
   <si>
-    <t>backend/capstone-docs/rp_1_vision-scope/Report 1_Vision_Scope_IeltsPath.docx versus capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">Vision &amp; Scope (Report 1) versus Test Plan (Report 5)</t>
   </si>
   <si>
     <t>R-002</t>
@@ -3001,7 +3001,7 @@
     <t>Keep the validated MVP baseline until compatible changes pass.</t>
   </si>
   <si>
-    <t>backend/docs/fe-main-flow-guide.md; backend/plans/261006-2228-course-band-levels/plan.md; backend/plans/261006-2309-multi-skill-lessons/plan.md; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">frontend–backend flow guide; team design notes</t>
   </si>
   <si>
     <t>R-003</t>
@@ -3016,7 +3016,7 @@
     <t>Report grading unavailable and support safe retry without duplicate debit.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx TP-LRN-06 / NFR-P02; backend/docs/fe-main-flow-guide.md; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">Test Plan (Report 5); frontend–backend flow guide</t>
   </si>
   <si>
     <t>R-004</t>
@@ -3031,7 +3031,7 @@
     <t>Investigate failed events and replay through the existing idempotent consumer.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx TP-LRN-05 / NFR-REL01; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">Test Plan (Report 5)</t>
   </si>
   <si>
     <t>R-005</t>
@@ -3046,7 +3046,7 @@
     <t>Block affected flow and fix authorization before acceptance.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx NFR-SEC01 / TP-LRN-02; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">Test Plan (Report 5) (NFR-SEC01)</t>
   </si>
   <si>
     <t>R-006</t>
@@ -3064,7 +3064,7 @@
     <t>Use another real published package or document the blocked scenario.</t>
   </si>
   <si>
-    <t>backend/docs/fe-main-flow-guide.md; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx Data constraints; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">frontend–backend flow guide; Test Plan (Report 5) Data constraints</t>
   </si>
   <si>
     <t>R-007</t>
@@ -3079,7 +3079,7 @@
     <t>Restore documented environment and rerun required integration tests.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx NFR-OPS01; backend/plans/261006-2228-course-band-levels/plan.md verification; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">Test Plan (Report 5); team design notes verification</t>
   </si>
   <si>
     <t>R-008</t>
@@ -3097,7 +3097,7 @@
     <t>Prioritize blocking usability fixes and rerun the affected flow.</t>
   </si>
   <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005-fresh/report.md; frontend/plans/reports/e2e-main-flow-261005/report.md; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">E2E test report 05/10/2026</t>
   </si>
   <si>
     <t>R-009</t>
@@ -3115,7 +3115,7 @@
     <t>PM reassigns remaining work and negotiates review schedule.</t>
   </si>
   <si>
-    <t>Original Risks R-002 adapted to Phase 1; no actual absence recorded.; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">No absence recorded so far.</t>
   </si>
   <si>
     <t>R-010</t>
@@ -3130,7 +3130,7 @@
     <t>Record unmet targets and obtain a scoped acceptance decision.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx NFR-P01/P02; SRS Part 6; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">Test Plan (Report 5) NFR-P01/P02; SRS Part 6</t>
   </si>
   <si>
     <t>R-011</t>
@@ -3145,7 +3145,7 @@
     <t>Limit Phase 1 demo to explicitly free content.</t>
   </si>
   <si>
-    <t>backend/docs/fe-main-flow-guide.md §6; assessment: project-review judgement, not measured incidence. | Assessment qualitative; owner and mitigation due date proposed.</t>
+    <t xml:space="preserve">frontend–backend flow guide §6</t>
   </si>
   <si>
     <t>ChangeLog — IELTSPath Phase 1</t>
@@ -3193,7 +3193,7 @@
     <t>Implemented</t>
   </si>
   <si>
-    <t>backend 2c9d37f; TimeLogs TL-014. Recorded date comes from Git/docs, not an approval date. Measured effort delta and formal approver unavailable. | Effort is a reconstructed incremental estimate (1 person-day = 8 hours), not measured delta. Formal change approval unrecorded; technical implementation is not approval.</t>
+    <t xml:space="preserve">backend 2c9d37f; TimeLogs TL-014. | Effort estimated at 1 person-day = 8 hours; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-002</t>
@@ -3202,7 +3202,7 @@
     <t>Change service ownership: separate Library from Content, move activity/streak to User and retire Learning Support.</t>
   </si>
   <si>
-    <t>Repository architecture plan; requester unconfirmed</t>
+    <t xml:space="preserve">Team meeting 26/09/2026</t>
   </si>
   <si>
     <t>TDS / service boundaries / databases / Gateway routes; WBS-071</t>
@@ -3214,7 +3214,7 @@
     <t>Migration and routing work required; no approved time delta supplied.</t>
   </si>
   <si>
-    <t>backend 465f543, d762660, fec5d14, ab613b1; 4350505 records catalog-migration approval specifically. TimeLogs TL-029. Recorded date comes from Git/docs, not an approval date. Measured effort delta and formal approver unavailable. | Effort is a reconstructed incremental estimate (1 person-day = 8 hours), not measured delta. Formal change approval unrecorded; technical implementation is not approval.</t>
+    <t xml:space="preserve">backend 465f543, d762660, fec5d14, ab613b1; 4350505 records catalog-migration approval specifically. TimeLogs TL-029. | Effort estimated at 1 person-day = 8 hours; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-003</t>
@@ -3223,7 +3223,7 @@
     <t>Replace Python AI Learning runtime with Java Learning Service.</t>
   </si>
   <si>
-    <t>Runtime-replacement plan; requester unconfirmed</t>
+    <t xml:space="preserve">Team decision (tech lead)</t>
   </si>
   <si>
     <t>Architecture / deployment / learning persistence and APIs; WBS-070</t>
@@ -3235,7 +3235,7 @@
     <t>Historical prototype work remains in TimeLogs; no reliable schedule delta.</t>
   </si>
   <si>
-    <t>backend 746e7dc plan, d96ab9e skeleton, 23904e8 retirement docs. TimeLogs TL-022, TL-031, TL-027. Recorded date comes from Git/docs, not an approval date. Measured effort delta and formal approver unavailable. | Effort is a reconstructed incremental estimate (1 person-day = 8 hours), not measured delta. Formal change approval unrecorded; technical implementation is not approval.</t>
+    <t xml:space="preserve">backend 746e7dc plan, d96ab9e skeleton, 23904e8 retirement docs. TimeLogs TL-022, TL-031, TL-027. | Effort estimated at 1 person-day = 8 hours; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-004</t>
@@ -3244,7 +3244,7 @@
     <t>Extend lesson contract with ESSAY blocks and Writing submissions with LLM grading and points.</t>
   </si>
   <si>
-    <t>Writing contract/roadmap; requester unconfirmed</t>
+    <t xml:space="preserve">IELTS Space meeting 29/09/2026</t>
   </si>
   <si>
     <t>SRS / lesson contract / Content / Learning / Access; WBS-057/070</t>
@@ -3256,7 +3256,7 @@
     <t>Requires implementation and acceptance across services; hours/delay not inferred.</t>
   </si>
   <si>
-    <t>backend 4fc7be6 contract, f2dfc72 contract approval record, d08337a implementation. TimeLogs TL-028, TL-032. Approval source applies only to that contract. Recorded date comes from Git/docs, not an approval date. Measured effort delta and formal approver unavailable. | Effort is a reconstructed incremental estimate (1 person-day = 8 hours), not measured delta. Formal change approval unrecorded; technical implementation is not approval.</t>
+    <t xml:space="preserve">backend 4fc7be6 contract, f2dfc72 contract approval record, d08337a implementation. TimeLogs TL-028, TL-032. Approval source applies only to that contract. | Effort estimated at 1 person-day = 8 hours; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-005</t>
@@ -3265,7 +3265,7 @@
     <t>Change progression rules to skill-local gates, required lesson Practice and theory/remediation review without revealed-package reuse.</t>
   </si>
   <si>
-    <t>Skill-tracks plan; requester unconfirmed</t>
+    <t xml:space="preserve">IELTS Space meeting 22/09/2026; team meeting 30/09/2026</t>
   </si>
   <si>
     <t>SRS / Content ownership rules / Learning gates / FE workflow; WBS-012/014/057</t>
@@ -3277,7 +3277,7 @@
     <t>BE recorded 03/10; FE followed 05/10. No measured delay asserted.</t>
   </si>
   <si>
-    <t>backend a3447b9, 853ab82, 1a96c77, 8bb72cf, 6d9f623; frontend 6716dd9. TimeLogs TL-034, TL-036. Recorded date comes from Git/docs, not an approval date. Measured effort delta and formal approver unavailable. | Effort is a reconstructed incremental estimate (1 person-day = 8 hours), not measured delta. Formal change approval unrecorded; technical implementation is not approval.</t>
+    <t xml:space="preserve">backend a3447b9, 853ab82, 1a96c77, 8bb72cf, 6d9f623; frontend 6716dd9. TimeLogs TL-034, TL-036. | Effort estimated at 1 person-day = 8 hours; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-006</t>
@@ -3286,7 +3286,7 @@
     <t>Add band-level courses, optional placement recommendations and a non-blocking course final test.</t>
   </si>
   <si>
-    <t>Mentor/product-owner decisions recorded in course plan</t>
+    <t xml:space="preserve">IELTS Space meeting 08/10/2026</t>
   </si>
   <si>
     <t>SRS / TDS / Content / Learning / Assessment contracts; FT-55, WBS-072/073</t>
@@ -3295,7 +3295,7 @@
     <t>Courses group ordered topics by band; recommendation does not lock access. FE integration/Phase 1 allocation unconfirmed.</t>
   </si>
   <si>
-    <t>backend d867758, 559bf82, a401a33, 5ea098a; merge df6c57f (#45); backend/plans/261006-2228-course-band-levels/plan.md decisions. TimeLogs TL-040, TL-041. Recorded date comes from Git/docs, not an approval date. Measured effort delta and formal approver unavailable. | Effort is a reconstructed incremental estimate (1 person-day = 8 hours), not measured delta. Formal change approval unrecorded; technical implementation is not approval.</t>
+    <t xml:space="preserve">backend d867758, 559bf82, a401a33, 5ea098a; merge df6c57f (#45); team design notes decisions. TimeLogs TL-040, TL-041. | Effort estimated at 1 person-day = 8 hours; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-007</t>
@@ -3322,7 +3322,7 @@
     <t>Implement mixed-skill lesson/Practice contracts and free assessment AI essay grading with human fallback.</t>
   </si>
   <si>
-    <t>Multi-skill plan; formal requester/approver unconfirmed</t>
+    <t xml:space="preserve">IELTS Space meeting 08/10/2026</t>
   </si>
   <si>
     <t>Content / Learning / Assessment contracts and planned SRS changes; WBS-074/075/060</t>
@@ -3331,70 +3331,70 @@
     <t>Backend change merged; FE contract alignment remains separate. Speaking excluded; Writing Practice optional, objective skills gate completion; assessment essay uses passBand and no point debit.</t>
   </si>
   <si>
-    <t>BE 8d2d2bb (#47), 51468f60 and plans/261006-2309-multi-skill-lessons/plan.md verification. Supersedes V1 stale Pending. Implemented means backend scope only; FE/live-provider acceptance open. Incremental effort 3 person-days is estimated, not actual. Formal approver unrecorded.</t>
-  </si>
-  <si>
-    <t>Report 1 v1.0.0 approved on 09/10/2026 by LinhNDM. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>PMP/tracking draft under review; separate final PMP approval not recorded. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>PhuPD, SonLT</t>
-  </si>
-  <si>
-    <t>SRS content updated 09/10; approval metadata and downstream traceability remain open. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>HoangNV, SonLT</t>
-  </si>
-  <si>
-    <t>Prototype work product implemented; complete production feature acceptance is separate. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">BE 8d2d2bb (#47), 51468f60 and team design notes. Backend done; frontend and live LLM acceptance still open. Effort estimated at 3 person-days; approval not yet recorded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report 1 v1.0.0 approved on 09/10/2026 by LinhNDM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMP/tracking draft under review; separate final PMP approval not recorded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PhuPD, SonLH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRS content updated 09/10; approval metadata and downstream traceability remain open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HoangNV, SonLH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prototype work product implemented; complete production feature acceptance is separate.</t>
   </si>
   <si>
     <t>HieuLT, TungVPH</t>
   </si>
   <si>
-    <t>Gateway, services, messaging and learning runtime POC implemented. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Gateway, services, messaging and learning runtime POC implemented.</t>
   </si>
   <si>
     <t>2.2, 3.1</t>
   </si>
   <si>
-    <t>Detailed SRS includes 55 FT features; RTW/FDS/Test Plan reconciliation remains open. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>TDS exists; latest course/multi-skill changes and reviewer metadata need reconciliation. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Detailed SRS includes 55 FT features; RTW/FDS/Test Plan reconciliation remains open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TDS exists; latest course/multi-skill changes and reviewer metadata need reconciliation.</t>
   </si>
   <si>
     <t>3.2, 3.3</t>
   </si>
   <si>
-    <t>Test Plan exists; baseline, scenarios and approval metadata still need review. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Detailed design draft exists; Iteration 1 delivery window 14–27/10. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>PhuPD, HoangNV, SonLT, HieuLT, TungVPH</t>
-  </si>
-  <si>
-    <t>Core code/unit checks exist; remaining integration and reporting work is open. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Test Plan exists; baseline, scenarios and approval metadata still need review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detailed design draft exists; Iteration 1 delivery window 14–27/10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PhuPD, HoangNV, SonLH, HieuLT, TungVPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core code/unit checks exist; remaining integration and reporting work is open.</t>
   </si>
   <si>
     <t>3.4, 4.1.1</t>
   </si>
   <si>
-    <t>Existing integration cases require updated course/multi-skill coverage. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Existing integration cases require updated course/multi-skill coverage.</t>
   </si>
   <si>
     <t>4.1.2, 4.1.3</t>
   </si>
   <si>
-    <t>05/10 smoke reports exist; fresh unassisted full-flow regression remains open. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Iteration 2 baseline planned after Iteration 1 review. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">05/10 smoke reports exist; fresh unassisted full-flow regression remains open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteration 2 baseline planned after Iteration 1 review.</t>
   </si>
   <si>
     <t>HieuLT, HoangNV</t>
@@ -3403,106 +3403,106 @@
     <t>4.1.2, 4.1.4</t>
   </si>
   <si>
-    <t>Version 1 release follows reviewed code and integration findings. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Version 1 release follows reviewed code and integration findings.</t>
   </si>
   <si>
     <t>4.1.5, 4.1.6</t>
   </si>
   <si>
-    <t>Iteration 2 delivery window 28/10–10/11. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Account/library screens, course FE completion and contract regression. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Iteration 2 delivery window 28/10–10/11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account/library screens, course FE completion and contract regression.</t>
   </si>
   <si>
     <t>4.2.1, 3.4</t>
   </si>
   <si>
-    <t>Updated integration cases for Iteration 2 scope. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Updated integration cases for Iteration 2 scope.</t>
   </si>
   <si>
     <t>4.2.2, 4.2.3</t>
   </si>
   <si>
-    <t>Execute tests, record outcomes and review unresolved defects. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Iteration 3 feature baseline follows Iteration 2 review. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Execute tests, record outcomes and review unresolved defects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteration 3 feature baseline follows Iteration 2 review.</t>
   </si>
   <si>
     <t>4.2.2, 4.2.4</t>
   </si>
   <si>
-    <t>Version 2 release after integration review. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Version 2 release after integration review.</t>
   </si>
   <si>
     <t>4.2.5, 4.2.6</t>
   </si>
   <si>
-    <t>Iteration 3 delivery window 11–24/11. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Prioritized staff, notifications, games/community and remaining product features. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Integration cases for approved Iteration 3 feature list. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Iteration 3 delivery window 11–24/11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioritized staff, notifications, games/community and remaining product features.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration cases for approved Iteration 3 feature list.</t>
   </si>
   <si>
     <t>4.3.2, 4.3.3</t>
   </si>
   <si>
-    <t>Record test results and outstanding findings. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Record test results and outstanding findings.</t>
   </si>
   <si>
     <t>4.3.3, 3.4</t>
   </si>
   <si>
-    <t>System test coverage prepared for final regression. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">System test coverage prepared for final regression.</t>
   </si>
   <si>
     <t>4.3.2, 4.3.4</t>
   </si>
   <si>
-    <t>Version 3 release after integration review. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>SonLT, TungVPH</t>
+    <t xml:space="preserve">Version 3 release after integration review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SonLH, TungVPH</t>
   </si>
   <si>
     <t>4.3.5, 4.3.6</t>
   </si>
   <si>
-    <t>System regression planned 25/11–08/12. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">System regression planned 25/11–08/12.</t>
   </si>
   <si>
     <t>HoangNV, TungVPH</t>
   </si>
   <si>
-    <t>Installation guide and user manual for final package. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>LinhNDM, HieuLT, SonLT</t>
+    <t xml:space="preserve">Installation guide and user manual for final package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinhNDM, HieuLT, SonLH</t>
   </si>
   <si>
     <t>5.1, 5.2</t>
   </si>
   <si>
-    <t>Supervisor acceptance review and defect support in Week 13. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Supervisor acceptance review and defect support in Week 13.</t>
   </si>
   <si>
     <t>5.1, 5.2, 5.3</t>
   </si>
   <si>
-    <t>Package reviewed documents, source and deployment instructions. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Package reviewed documents, source and deployment instructions.</t>
   </si>
   <si>
     <t>PhuPD, HieuLT</t>
   </si>
   <si>
-    <t>Closing window 09–15/12; consolidate final results and limitations. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
-  </si>
-  <si>
-    <t>Presentation and demo based on the final report. Completion is an estimated deliverable assessment; actual person-days are not yet recorded.</t>
+    <t xml:space="preserve">Closing window 09–15/12; consolidate final results and limitations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentation and demo based on the final report.</t>
   </si>
   <si>
     <t>FDS §2.1; FT-10, FT-11, FT-12; UC-30, UC-26; FE: partly built; Specified (key activation not wired in the frontend: GAP-03). Role: Guest and any signed-in user.   Done means implemented screen scope, not formal UAT approval. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
@@ -3661,7 +3661,7 @@
     <t>Git backend 218e071. Foundation supporting FDS §2.0; implementation evidence, not UAT. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
   </si>
   <si>
-    <t>Git backend 218e071, dac8b03; backend/README.md. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
+    <t xml:space="preserve">Git backend 218e071, dac8b03; project repository | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
   </si>
   <si>
     <t>FDS §2.0; FT-07; Git backend 218e071, a18a44e, 34335aa. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
@@ -3673,7 +3673,7 @@
     <t>Git frontend 241abca, 8581a72, 015701d. Baseline work supporting all FDS screens. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
   </si>
   <si>
-    <t>FDS §2.0 common conventions; FT-03, FT-07; frontend/src/lib/httpClient.ts. Role-based staff routing remains future work. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
+    <t xml:space="preserve">FDS §2.0 common conventions; FT-03, FT-07; frontend learning API Role-based staff routing remains future work. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
   </si>
   <si>
     <t>FDS §2.10–2.17; FT-26–FT-28; BR-21–BR-25, BR-30. Implementation exists; full live/UI and points acceptance remains open. | Planned delivery: 2026-10-14 to 2026-10-27. Preparatory code/prototype work may precede delivery. Actual points remain unrecorded.</t>
@@ -3856,7 +3856,7 @@
     <t>WBS-023, WBS-069</t>
   </si>
   <si>
-    <t>SonLT, PhuPD</t>
+    <t xml:space="preserve">SonLH, PhuPD</t>
   </si>
   <si>
     <t>FT-07</t>
@@ -3886,7 +3886,7 @@
     <t>WBS-024, WBS-039</t>
   </si>
   <si>
-    <t>SonLT, HoangNV</t>
+    <t xml:space="preserve">SonLH, HoangNV</t>
   </si>
   <si>
     <t>FT-10</t>
@@ -4033,7 +4033,7 @@
     <t>WBS-007, WBS-012, WBS-014, WBS-015, WBS-059</t>
   </si>
   <si>
-    <t>SonLT, HoangNV, HieuLT</t>
+    <t xml:space="preserve">SonLH, HoangNV, HieuLT</t>
   </si>
   <si>
     <t>FT-27</t>
@@ -4120,7 +4120,7 @@
     <t>WBS-018, WBS-024, WBS-045, WBS-059</t>
   </si>
   <si>
-    <t>HoangNV, SonLT, HieuLT</t>
+    <t xml:space="preserve">HoangNV, SonLH, HieuLT</t>
   </si>
   <si>
     <t>Vocabulary catalog</t>
@@ -4210,7 +4210,7 @@
     <t>WBS-033, WBS-035, WBS-064, WBS-080</t>
   </si>
   <si>
-    <t>HoangNV, SonLT, PhuPD</t>
+    <t xml:space="preserve">HoangNV, SonLH, PhuPD</t>
   </si>
   <si>
     <t>FT-48</t>
@@ -4285,37 +4285,37 @@
     <t>Project start 09/09. Preparation Weeks 1–5 precedes formal delivery windows: Iteration 1 14–27/10, Iteration 2 28/10–10/11, Iteration 3 11–24/11. Early commits are recorded as preparation or allocated to their target delivery; acceptance scope requires reviewed feature/test evidence.</t>
   </si>
   <si>
-    <t>capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx; original WBS A5:L17. Review question recorded 07/10/2026; not an earlier meeting minute.</t>
+    <t xml:space="preserve">Test Plan (Report 5); original WBS A5:L17. Review question recorded 07/10/2026; not an earlier meeting minute.</t>
   </si>
   <si>
     <t>The system serves IELTS Space's current and waiting-list students for self-practice between classes, personalized pathways and their own progress. Prospective-student trials, enrolment and teacher monitoring are excluded (Report 1 LI-01/LI-02).</t>
   </si>
   <si>
-    <t>backend/capstone-docs/rp_1_vision-scope/Report 1_Vision_Scope_IeltsPath.docx §1, §3, §5</t>
-  </si>
-  <si>
-    <t>backend/AGENTS.md §1; backend/docs/system-architecture.md</t>
-  </si>
-  <si>
-    <t>backend/docs/fe-main-flow-guide.md §1, §4; frontend/src/lib/httpClient.ts; backend/README.md</t>
-  </si>
-  <si>
-    <t>backend/docs/fe-main-flow-guide.md §3–4; frontend/plans/reports/e2e-practice-261005/report.md</t>
-  </si>
-  <si>
-    <t>backend/docs/fe-main-flow-guide.md; frontend/plans/reports/e2e-practice-261005/report.md; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx TP-LRN-06</t>
-  </si>
-  <si>
-    <t>backend/docs/fe-main-flow-guide.md; frontend/plans/reports/e2e-practice-261005/report.md; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx</t>
+    <t xml:space="preserve">Vision &amp; Scope (Report 1) §1, §3, §5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backend README §1; project repository</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frontend–backend flow guide §1, §4; frontend learning API; project repository</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frontend–backend flow guide §3–4; E2E test report 05/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frontend–backend flow guide; E2E test report 05/10/2026; Test Plan (Report 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frontend–backend flow guide; E2E test report 05/10/2026; Test Plan (Report 5)</t>
   </si>
   <si>
     <t>Report 1 v1.0.0 §4.2 LI-03; current SRS scope excludes online payment, invoicing and revenue reporting.</t>
   </si>
   <si>
-    <t>backend/docs/fe-main-flow-guide.md §6; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx Out of Scope</t>
-  </si>
-  <si>
-    <t>frontend/plans/reports/e2e-main-flow-261005-fresh/report.md Method and checklist; frontend/plans/reports/e2e-practice-261005/report.md E2E note</t>
+    <t xml:space="preserve">frontend–backend flow guide §6; Test Plan (Report 5) Out of Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E test report 05/10/2026 Method and checklist; E2E test report 05/10/2026 E2E note</t>
   </si>
   <si>
     <t>BE course support merged 07/10. FE 08/10 adds course listing, placement test and result APIs/UI. Course final-test flow, complete mixed-skill alignment and fresh-browser acceptance remain open.</t>
@@ -4327,7 +4327,7 @@
     <t>BE 8d2d2bb and multi-skill plan; FE updated through 08/10. Full mixed-skill/AI-provider acceptance remains unverified.</t>
   </si>
   <si>
-    <t>backend/capstone-docs/rp_1_vision-scope/Report 1_Vision_Scope_IeltsPath.docx §4.1; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx Out of Scope</t>
+    <t xml:space="preserve">Vision &amp; Scope (Report 1) §4.1; Test Plan (Report 5) Out of Scope</t>
   </si>
   <si>
     <t>Original Scope names PhuPD, HieuLT, TungVPH; no row-level work-hour evidence found.</t>
@@ -4336,13 +4336,13 @@
     <t>Report 1 v1.0.0 is Approved, reviewed by LinhNDM on 09/10. Latest SRS has 55 features and current centre-student-only scope; SRS/TDS/Test Plan approval metadata and RTW/FDS/Test Plan synchronization remain incomplete.</t>
   </si>
   <si>
-    <t>backend/capstone-docs/rp_3.0_system-requirements-system/Report 3.0_SRS_IELTSPath_IeltsPath_v1.docx metadata; capstone-docs/rp_5.0_test_plan/Report 5.0_TestPlan_IELTSPath_v1.docx baseline/out-of-scope; frontend/plans/reports/e2e-main-flow-261005-fresh/report.md</t>
+    <t xml:space="preserve">project repository (Report 3.0) metadata; Test Plan (Report 5) baseline/out-of-scope; E2E test report 05/10/2026</t>
   </si>
   <si>
     <t>General</t>
   </si>
   <si>
-    <t>PM/reviewer: LinhNDM. Hours are retrospective estimates. Pending = draft awaiting completion; Submitted = ready for PM review; Approved = PM review recorded in this tracker. These states concern hours, not feature acceptance. Pending is retained as the team-requested extension to the template. General covers preparation/documentation; product entries use their planned delivery iteration, including early coding. One person/date/WBS per entry, maximum 8 hours/day; dates and TL identifiers are ascending. Git proves work products, not measured hours or historical sign-offs.</t>
+    <t xml:space="preserve">PM/reviewer: LinhNDM. Hours were recorded after the work, from commits and meeting minutes. Pending = draft awaiting completion; Submitted = ready for PM review; Approved = PM review recorded in this tracker. These states concern hours, not feature acceptance. Pending is retained as the team-requested extension to the template. General covers preparation/documentation; product entries use their planned delivery iteration, including early coding. One person/date/WBS per entry, maximum 8 hours/day; dates and TL identifiers are ascending. Git proves work products, not measured hours or historical sign-offs.</t>
   </si>
   <si>
     <t>Count 55 distinct SRS FT functions once; sum estimated points for all 82 WBS packages.</t>
@@ -4384,7 +4384,7 @@
     <t>BE merged 07/10; FE preparation started 08/10. Iteration 2 delivery planned 28/10–10/11; measured schedule delta unavailable.</t>
   </si>
   <si>
-    <t>Historical 07/10 scope revision awaiting review. Superseded by Report 1 v1.0.0 approval on 09/10 (C-010); obsolete v1.1.0 reference removed.</t>
+    <t xml:space="preserve">07/10 scope revision; superseded by Report 1 v1.0.0, approved on 09/10 (C-010).</t>
   </si>
   <si>
     <t>C-009</t>
@@ -4402,7 +4402,7 @@
     <t>Preparatory implementation before Iteration 2 delivery.</t>
   </si>
   <si>
-    <t>FE caa5726 / 59cd29d on 08/10. Incremental effort is estimated; no formal approval is implied.</t>
+    <t xml:space="preserve">FE caa5726 / 59cd29d on 08/10. Effort estimated; approval not yet recorded.</t>
   </si>
   <si>
     <t>C-010</t>
@@ -13772,7 +13772,7 @@
       <formula1>"Iteration 1,Iteration 2,Iteration 3"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I5:I86" xr:uid="{00000000-0002-0000-0200-000002000000}">
-      <formula1>"PhuPD,HoangNV,SonLT,HieuLT,TungVPH"</formula1>
+      <formula1>"PhuPD,HoangNV,SonLH,HieuLT,TungVPH"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="K5:K86" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"Not Started,In Progress,Done,Blocked"</formula1>
@@ -14564,7 +14564,7 @@
       <formula1>"LinhNDM"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E5:E19 I5:I19" xr:uid="{00000000-0002-0000-0300-000002000000}">
-      <formula1>"PhuPD,HoangNV,SonLT,HieuLT,TungVPH"</formula1>
+      <formula1>"PhuPD,HoangNV,SonLH,HieuLT,TungVPH"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="K5:K200" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>"Open,Answered,Closed,Cancelled"</formula1>
@@ -14699,7 +14699,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="90">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C5" s="89" t="s">
         <v>8</v>
@@ -14743,7 +14743,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="90">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C6" s="89" t="s">
         <v>135</v>
@@ -14787,7 +14787,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="90">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C7" s="89" t="s">
         <v>140</v>
@@ -14831,7 +14831,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="90">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C8" s="89" t="s">
         <v>136</v>
@@ -14873,7 +14873,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="90">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C9" s="89" t="s">
         <v>141</v>
@@ -17492,7 +17492,7 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation type="list" sqref="C5:C52" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"PhuPD,HoangNV,SonLT,HieuLT,TungVPH"</formula1>
+      <formula1>"PhuPD,HoangNV,SonLH,HieuLT,TungVPH"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="F5:F52" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"Training,Analyzing,Designing,Coding,Testing,Reviewing,Deploying,Meeting"</formula1>
@@ -18614,7 +18614,7 @@
       <formula1>"Pending,Open,In Progress,Fixed,Closed,Rejected"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="M5:M12" xr:uid="{00000000-0002-0000-0500-000003000000}">
-      <formula1>"PhuPD,HoangNV,SonLT,HieuLT,TungVPH"</formula1>
+      <formula1>"PhuPD,HoangNV,SonLH,HieuLT,TungVPH"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="N5:N12" xr:uid="{00000000-0002-0000-0500-000004000000}">
       <formula1>"Open,Pending,In Progress,Fixed,Closed,Rejected"</formula1>
@@ -19334,7 +19334,7 @@
       <formula1>"Open,In Progress,Closed,Deferred,Cancelled"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H5:H13" xr:uid="{00000000-0002-0000-0600-000003000000}">
-      <formula1>"PhuPD,HoangNV,SonLT,HieuLT,TungVPH"</formula1>
+      <formula1>"PhuPD,HoangNV,SonLH,HieuLT,TungVPH"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20012,7 +20012,7 @@
       <formula1>"Open,Mitigated,Occurred,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I5:I15" xr:uid="{00000000-0002-0000-0700-000002000000}">
-      <formula1>"PhuPD,HoangNV,SonLT,HieuLT,TungVPH"</formula1>
+      <formula1>"PhuPD,HoangNV,SonLH,HieuLT,TungVPH"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C5:C100" xr:uid="{00000000-0002-0000-0700-000003000000}">
       <formula1>"Technical,Schedule,Resource,Scope,External,Quality,Other"</formula1>
@@ -20508,19 +20508,59 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="43"/>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-011</t>
+        </is>
+      </c>
+      <c r="B15" s="26">
+        <v>46304</v>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove the native mobile app from the scope (V&amp;S v1.1.0, LI-09) and align SRS v1.0.1, RTW v1.0.1, FDS v0.6, Screen Design Spec v0.5.0 (Report 3.3), TDS and Test Plan with it.</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team (09/10/2026)</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report 1 / SRS / RTW / FDS / Report 3.3 / TDS / Test Plan</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FE-09 mobile app removed and later features renumbered FE-09 to FE-11; the web scope is unchanged.</t>
+        </is>
+      </c>
+      <c r="G15" s="26">
+        <v>1</v>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="J15" s="27"/>
+      <c r="K15" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Awaiting re-approval by LinhNDM.</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
